--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KVAL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SYSTEM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CLUBS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SERIES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NOTES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="META" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TODO" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +34,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,8 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1509,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,6 +1559,36 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>parent_node_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>feeds_into</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>feeds_into_loser</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2246,6 +2294,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2407,4 +2456,79 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0002</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'Kvalifikace o ligu'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -905,7 +905,7 @@
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -1775,9 +1775,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0007</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1812,9 +1817,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0008</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1886,9 +1896,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0010</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1923,9 +1938,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0004</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1960,9 +1980,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0009</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1997,9 +2022,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0003</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2034,9 +2064,14 @@
           <t>L10</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CLUB_S1947_48_0001</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Republiková úroveň z Wiki (en). Prev_club_id nevyplněn (S1947_48 zatím nezpracována).</t>
+          <t>prev_club_id doplněn ze S1947_48 (nejvyšší soutěž z PDF).</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2270,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,7 +2329,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -1527,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -15,6 +15,7 @@
     <sheet name="NOTES" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="META" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="TODO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30STRC" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TODO'!$A$1:$F$2</definedName>
@@ -1527,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +1688,134 @@
           <t>NODE_S1948_49_0002</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30_Středočeská divize</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30_Středočeská divize Skupina A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0004</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30_Středočeská divize Skupina B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0004</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1699,7 +1828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1767,7 +1896,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LTC Praha [M]</t>
+          <t>JTO Sokol Pražský (LTC Praha)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1814,7 +1943,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ŠK Bratislava</t>
+          <t>ZJ Sokol NV Bratislava</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1893,7 +2022,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AC Stadion České Budějovice</t>
+          <t>JTO Sokol Stadion České Budějovice</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1935,7 +2064,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sokol Zbrojovka Židenice</t>
+          <t>ZSJ Zbrojovka Brno-Židenice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1977,7 +2106,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AC Sparta Bubeneč</t>
+          <t>JTO Sokol Sparta Bubeneč</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2019,7 +2148,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sokol Prostějov</t>
+          <t>JTO Sokol II Prostějov</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2061,7 +2190,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I. ČLTK Praha</t>
+          <t>JTO Sokol I Praha (I. ČLTK Praha)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2235,6 +2364,566 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>Pardubice</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sokol Černošice</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JTO Sokol Černošice</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Černošice</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sokol Záběhlice-Zbraslav</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JTO Sokol Záběhlice-Zbraslav</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sokol Slavia Praha</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JTO Sokol Slavia Praha</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sokol Libeň</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JTO Sokol Libeň</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sokol Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JTO Sokol Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Roudnice nad Labem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sokol Kročehlavy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JTO Sokol Kročehlavy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sokol II Smíchov</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JTO Sokol II Smíchov</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sokol Hostivař</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JTO Sokol Hostivař</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ZSJ Kara Starý Kolín</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ZSJ Kara Starý Kolín</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Starý Kolín</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sokol Říčany</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JTO Sokol Říčany</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Říčany</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sokol Velké Popovice</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JTO Sokol Velké Popovice</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Velké Popovice</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sokol Modrobílí Kolín</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JTO Sokol Modrobílí Kolín</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kolín</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sokol Vršovice-Bohemians</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JTO Sokol Vršovice-Bohemians</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Praha</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sokol Čelákovice</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JTO Sokol Čelákovice</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Čelákovice</t>
         </is>
       </c>
     </row>
@@ -2315,7 +3004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,14 +3017,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Republiková úroveň (extraliga + kvalifikace o ligu) zpracována z Wikipedie (en).</t>
+          <t>Nejvyšší soutěž (Státní liga) i divize zpracovány z PDF (dobový tisk).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Krajské a okresní soutěže 1948/49 ZATÍM NEZPRACOVÁNY — Wiki nepokrývá regiony, čeká na podklady.</t>
+          <t>31. 3. 1948 sjednocení všech tělovýchovných organizací pod JTO Sokol — odtud sokolské názvy klubů (raw_name).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. 11. 1948: sloučení JTO Sokol Horácká Slavia Třebíč se ZSJ Zbrojovka Brno-Židenice; nový klub pod hlavičkou Zbrojovky převzal hráče i práva na Státní ligu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9. 11. 1948: po odchodu všech hráčů ze Stadionu Podolí (do Sparty a I. ČLTK) klub vyřazen ze soutěže — JTO Sokol Stadion Podolí ukončil činnost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pražské oddíly (LTC, ATK, Sparta, I. ČLTK) hrály doma na ZS Štvanice; Prostějov v Olomouci; Židenice na ZS Za Lužánkami.</t>
         </is>
       </c>
     </row>
@@ -2421,7 +3131,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wikipedia (en) — 1948-49 Czechoslovak Extraliga season</t>
+          <t>PDF sources/CZE1 + CZE2_3_nizsi (dobový tisk)</t>
         </is>
       </c>
     </row>
@@ -2481,7 +3191,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Šestý ročník. HC Stadion Podolí vyškrtnut (rozpad), nahrazen ATK Praha. Sokol Zbrojovka Židenice = sloučení Horácká Slavia Třebíč + Zbrojovka Židenice. I. ČLTK (finalista 1947/48) prohrál vše, 0 bodů.</t>
+          <t>Šestý ročník Státní ligy, 8 týmů jednokolově (mistr LTC Praha). Sokolské názvy (31.3.1948 sjednocení pod JTO Sokol). Stadion Podolí vyřazen 9.11.1948. Divize zpracovány po krajích.</t>
         </is>
       </c>
     </row>
@@ -2575,4 +3285,1264 @@
   <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol Černošice</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00101</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol Záběhlice-Zbraslav</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00102</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sokol Slavia Praha</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00103</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Libeň</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>28</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0016</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00104</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>23</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00105</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sokol Kročehlavy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00106</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sokol II Smíchov</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>43</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0005</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00107</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sokol Hostivař</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>67</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00108</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ZSJ Kara Starý Kolín</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>53</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00109</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sokol Říčany</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>41</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00110</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sokol Velké Popovice</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>37</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>38</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0023</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00111</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol Modrobílí Kolín</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0024</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00112</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sokol Vršovice-Bohemians</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0025</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00113</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sokol Čelákovice</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>78</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Středočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0006</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0026</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00114</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -16,6 +16,11 @@
     <sheet name="META" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="TODO" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="30STRC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30ZAPC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30VYCH" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30SVMR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30SVK" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30DIV" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TODO'!$A$1:$F$2</definedName>
@@ -1174,6 +1179,5475 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol Holoubkov</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0027</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00201</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol Čechie Horní Litvínov</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0028</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00202</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sokol Čechie Louny</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0029</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00203</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Viktoria Osek (u Rokycan)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0030</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00204</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol Volduchy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>37</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0031</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00205</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sokol Ústí nad Labem</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0032</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00206</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0033</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00207</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sokol Tábor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>19</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0034</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00208</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sokol Felbabka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0035</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00209</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sokol Horymír Neumětely</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>36</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0036</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00210</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sokol Blatná</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0037</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00211</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol Písek</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>40</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0038</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00212</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sokol Rožmitál pod Třemšínem</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Západočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0039</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00213</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00214</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0041</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00215</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZSJ Dekva Třebíč</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0042</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00216</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Svítkov</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0043</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00217</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol Choltice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0044</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00218</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0045</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00219</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sokol Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0046</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00220</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sokol Meteor Svobodné Dvory</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0047</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00221</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ZSJ VČE Slavia Hradec Králové</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0048</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00222</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sokol Sparta Kopidlno</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0049</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00223</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sokol Stadion Jaroměř</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>16</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0050</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00224</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol Dolní Bousov</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Východočeská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0051</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00225</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ZSJ Vítkovické železárny</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>44</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0052</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00226</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol Ostravská Slavia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0053</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00227</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZSJ Železničáři Vsetín</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0054</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00228</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Přerov</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0055</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00229</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol II Sparta Prostějov</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0056</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00230</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sokol Čechie VII Ostrava</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina A</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0057</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00231</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>79</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0058</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00232</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sokol Harnach Žižka Brno</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0059</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00233</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sokol Staroměstský</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0060</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00234</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZSJ Dyas Viktoria Uherský Ostroh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>22</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0061</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00235</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sokol Černá Hora</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>59</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0062</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00236</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol Slovácká Slavia Uherské Hradiště</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>76</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Moravskoslezská divize / Skupina B</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0063</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00237</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0064</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00238</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ZSJ Železničiari Zvolen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>22</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0065</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00239</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZJ Sokol VŠ Bratislava</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0066</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00240</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ZJ Sokol SNB Bratislava</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0067</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00241</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol Trenčín</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina západ</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0068</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00242</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>84</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0069</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00243</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sokol Sparta Prešov</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0070</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00244</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sokol Jednota Košice</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0071</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00245</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ZSJ Baťa Liptovský Mikuláš</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0072</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00246</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sokol Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>67</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga divize / Skupina východ</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0073</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00247</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>block_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>club_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comp_path</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>club_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dest_node_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>dest_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>season_fate</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tr_id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0033</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00248</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00249</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sokol Hostivař</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00250</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Černošice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00251</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina B</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0058</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00252</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ZSJ Vítkovické železárny</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina B</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0052</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00253</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Divize play-off / Semifinálová skupina B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0069</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00254</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Divize play-off / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M-divize</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Divize play-off / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0058</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00255</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZSJ Vítkovické železárny</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Divize play-off / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0052</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00256</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Divize play-off / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0033</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00257</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Divize play-off / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S1948_49_00258</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1528,7 +7002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,19 +7189,11 @@
           <t>REG_STC</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1760,18 +7226,11 @@
           <t>NODE_S1948_49_0004</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1804,18 +7263,695 @@
           <t>NODE_S1948_49_0004</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30_Západočeská divize</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>REG_ZPC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30_Západočeská Skupina A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>REG_ZPC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0007</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30_Západočeská Skupina B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>REG_ZPC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0007</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30_Východočeská divize</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30_Východočeská Skupina A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0010</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30_Východočeská Skupina B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0010</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30_Moravskoslezská divize</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30_Moravskoslezská Skupina A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30_Moravskoslezská Skupina B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0013</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30_Slovenská oblastná liga divize</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>REG_SVK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30_Slovenská oblastná liga Skupina západ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>REG_SVK</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0016</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30_Slovenská oblastná liga Skupina východ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>REG_SVK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0016</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Divize / celostátní play-off</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>playoff</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>REG_CS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Divize / Semifinálová skupina A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>final_group</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>REG_CS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Divize / Semifinálová skupina B</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>final_group</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>REG_CS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Divize / Finálová skupina</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>final_group</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>REG_CS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0019</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2-1-0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1828,7 +7964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2388,14 +8524,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2428,14 +8561,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2468,14 +8598,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2508,14 +8635,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2548,14 +8672,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2588,14 +8709,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2628,14 +8746,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2668,14 +8783,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2708,14 +8820,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2748,14 +8857,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2788,14 +8894,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2828,14 +8931,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2868,14 +8968,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2908,14 +9005,11 @@
           <t>30STRC</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Středočeská divize (PDF). prev_club_id zatím prázdný.</t>
@@ -2924,6 +9018,1886 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>Čelákovice</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sokol Holoubkov</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JTO Sokol Holoubkov</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Holoubkov</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sokol Čechie Horní Litvínov</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JTO Sokol Čechie Horní Litvínov</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Horní Litvínov</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sokol Čechie Louny</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JTO Sokol Čechie Louny</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Louny</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sokol Viktoria Osek (u Rokycan)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JTO Sokol Viktoria Osek (u Rokycan)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Osek</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sokol Volduchy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JTO Sokol Volduchy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Volduchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sokol Ústí nad Labem</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JTO Sokol Ústí nad Labem</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ústí nad Labem</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JTO Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>České Budějovice</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sokol Tábor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JTO Sokol Tábor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Tábor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sokol Felbabka</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JTO Sokol Felbabka</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Felbabka</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sokol Horymír Neumětely</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JTO Sokol Horymír Neumětely</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Neumětely</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sokol Blatná</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JTO Sokol Blatná</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Blatná</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sokol Písek</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JTO Sokol Písek</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Písek</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sokol Rožmitál pod Třemšínem</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>JTO Sokol Rožmitál pod Třemšínem</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Rožmitál pod Třemšínem</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JTO Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Pardubice</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sokol Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JTO Sokol Havlíčkův Brod</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZSJ Dekva Třebíč</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ZSJ Dekva Třebíč</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sokol Svítkov</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>JTO Sokol Svítkov</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Pardubice</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sokol Choltice</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>JTO Sokol Choltice</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Choltice</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JTO Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Okříšky</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sokol Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JTO Sokol Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Mladá Boleslav</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sokol Meteor Svobodné Dvory</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JTO Sokol Meteor Svobodné Dvory</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Svobodné Dvory</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ZSJ VČE Slavia Hradec Králové</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ZSJ VČE Slavia Hradec Králové</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Hradec Králové</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sokol Sparta Kopidlno</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JTO Sokol Sparta Kopidlno</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Kopidlno</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sokol Stadion Jaroměř</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JTO Sokol Stadion Jaroměř</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Jaroměř</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sokol Dolní Bousov</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JTO Sokol Dolní Bousov</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Dolní Bousov</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ZSJ Vítkovické železárny</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ZSJ Vítkovické železárny</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ostrava</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sokol Ostravská Slavia</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JTO Sokol Ostravská Slavia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ostrava</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ZSJ Železničáři Vsetín</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ZSJ Železničáři Vsetín</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Vsetín</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sokol Přerov</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JTO Sokol Přerov</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Přerov</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sokol II Sparta Prostějov</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JTO Sokol II Sparta Prostějov</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Prostějov</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sokol Čechie VII Ostrava</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JTO Sokol Čechie VII Ostrava</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ostrava</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Brno</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sokol Harnach Žižka Brno</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>JTO Sokol Harnach Žižka Brno</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Brno</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sokol Staroměstský</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JTO Sokol Staroměstský</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Staré Město</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ZSJ Dyas Viktoria Uherský Ostroh</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ZSJ Dyas Viktoria Uherský Ostroh</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Uherský Ostroh</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sokol Černá Hora</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>JTO Sokol Černá Hora</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sokol Slovácká Slavia Uherské Hradiště</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>JTO Sokol Slovácká Slavia Uherské Hradiště</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Uherské Hradiště</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sokol Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>JTO Sokol Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ZSJ Železničiari Zvolen</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ZSJ Železničiari Zvolen</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Zvolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ZJ Sokol VŠ Bratislava</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ZJ Sokol VŠ Bratislava</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ZJ Sokol SNB Bratislava</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ZJ Sokol SNB Bratislava</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sokol Trenčín</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>JTO Sokol Trenčín</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Trenčín</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>JTO Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Poprad</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sokol Sparta Prešov</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>JTO Sokol Sparta Prešov</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sokol Jednota Košice</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>JTO Sokol Jednota Košice</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ZSJ Baťa Liptovský Mikuláš</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ZSJ Baťa Liptovský Mikuláš</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Liptovský Mikuláš</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sokol Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JTO Sokol Spišská Nová Ves</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>30SVK</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Divize 1948/49 (PDF). prev_club_id zatím prázdný.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Spišská Nová Ves</t>
         </is>
       </c>
     </row>
@@ -2938,7 +10912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2992,6 +10966,246 @@
           <t>note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sokol II Meteor České Budějovice</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5:5, 2:1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1:0 (na zápasy)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Finále západočeské divize: mistr záp. divize</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0027</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sokol Holoubkov</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sokol Holoubkov</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5:5, 2:1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sokol I Pardubice</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8:0, 3:2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Finále východočeské divize: mistr vých. divize</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0102</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0046</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sokol Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sokol Mladá Boleslav</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8:0, 3:2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0103</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0069</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sokol Tatry Poprad</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6:4, 4:2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Finále slovenské divize: mistr slov. divize</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SER_S1948_49_0103</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1948_49_0064</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sokol Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sokol Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6:4, 4:2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3004,7 +11218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,6 +11260,48 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>Pražské oddíly (LTC, ATK, Sparta, I. ČLTK) hrály doma na ZS Štvanice; Prostějov v Olomouci; Židenice na ZS Za Lužánkami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Divize 1948/49: krajské skupiny A/B → krajská finále → celostátní play-off (Semifinálové skupiny A/B → Finálová skupina). VÍTĚZ DIVIZE: ZSJ GZ Královo Pole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Krajská finále: Západočeská — Meteor ČB (5:5, 2:1 nad Holoubkovem); Východočeská — Pardubice (8:0, 3:2 nad Ml. Boleslaví); Slovenská — Tatry Poprad (6:4, 4:2 nad B. Bystricí).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Slovenská oblastná liga — tabulky NEKOMPLETNÍ (nestejný počet zápasů, část výsledků neznámá); pořadí dle PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kvalifikace o divizi: vítězové župních I. tříd (Vokovice-Veleslavín, Čimice/Uhříněves, Stará Boleslav/Kyje aj.); postupující též Unhošť, Lokomotiva Nymburk, Viktoria Plzeň, Opava, Slovena Žilina, Kovosmalt Petržalka ad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Po sezóně: sloučení I. ČLTK + ZMP Praha, Ostravská Slavia + Sokol Mariánské Hory, Harnach Žižka Brno + Žabovřesky (soutěž přenechal Zbrojovce Brno-Židenice II.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Reorganizace po ročníku: zánikem župních mistrovství vznikly krajské soutěže.</t>
         </is>
       </c>
     </row>
@@ -3060,7 +11316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3167,7 +11423,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PARTIAL — pouze republiková úroveň (extraliga + kvalifikace). Regiony chybí.</t>
+          <t>Nejvyšší soutěž + kompletní divize (4 kraje + Slovensko) + celostátní play-off divize. Slovenské tabulky nekompletní. Župní I. třídy jen poznámky.</t>
         </is>
       </c>
     </row>
@@ -3204,6 +11460,18 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>Navázáno na S1949_50 (prev_club_id doplněn tam). Prev z S1947_48 zatím prázdný.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mistr_divize</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ZSJ GZ Královo Pole</t>
         </is>
       </c>
     </row>
@@ -3449,18 +11717,6 @@
           <t>Středočeská divize / Skupina A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>NODE_S1948_49_0005</t>
@@ -3471,13 +11727,6 @@
           <t>L20</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3485,7 +11734,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
@@ -3494,7 +11742,6 @@
           <t>Sokol Černošice</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>6</v>
       </c>
@@ -3541,16 +11788,11 @@
           <t>CLUB_S1948_49_0013</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>TR_S1948_49_00101</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3558,7 +11800,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>2</v>
       </c>
@@ -3567,7 +11808,6 @@
           <t>Sokol Záběhlice-Zbraslav</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>6</v>
       </c>
@@ -3614,16 +11854,11 @@
           <t>CLUB_S1948_49_0014</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>TR_S1948_49_00102</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3631,7 +11866,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>3</v>
       </c>
@@ -3640,7 +11874,6 @@
           <t>Sokol Slavia Praha</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>6</v>
       </c>
@@ -3687,16 +11920,11 @@
           <t>CLUB_S1948_49_0015</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>TR_S1948_49_00103</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3704,7 +11932,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>4</v>
       </c>
@@ -3713,7 +11940,6 @@
           <t>Sokol Libeň</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>6</v>
       </c>
@@ -3760,16 +11986,11 @@
           <t>CLUB_S1948_49_0016</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>TR_S1948_49_00104</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3777,7 +11998,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>5</v>
       </c>
@@ -3786,7 +12006,6 @@
           <t>Sokol Roudnice nad Labem</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>6</v>
       </c>
@@ -3833,16 +12052,11 @@
           <t>CLUB_S1948_49_0017</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>TR_S1948_49_00105</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3850,7 +12064,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>6</v>
       </c>
@@ -3859,7 +12072,6 @@
           <t>Sokol Kročehlavy</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>6</v>
       </c>
@@ -3906,16 +12118,11 @@
           <t>CLUB_S1948_49_0018</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>TR_S1948_49_00106</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3923,7 +12130,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>7</v>
       </c>
@@ -3932,7 +12138,6 @@
           <t>Sokol II Smíchov</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>6</v>
       </c>
@@ -3979,16 +12184,11 @@
           <t>CLUB_S1948_49_0019</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>TR_S1948_49_00107</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4001,18 +12201,6 @@
           <t>Středočeská divize / Skupina B</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>NODE_S1948_49_0006</t>
@@ -4023,13 +12211,6 @@
           <t>L20</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4037,7 +12218,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>1</v>
       </c>
@@ -4046,7 +12226,6 @@
           <t>Sokol Hostivař</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>6</v>
       </c>
@@ -4093,16 +12272,11 @@
           <t>CLUB_S1948_49_0020</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>TR_S1948_49_00108</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4110,7 +12284,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>2</v>
       </c>
@@ -4119,7 +12292,6 @@
           <t>ZSJ Kara Starý Kolín</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>6</v>
       </c>
@@ -4166,16 +12338,11 @@
           <t>CLUB_S1948_49_0021</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>TR_S1948_49_00109</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4183,7 +12350,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>3</v>
       </c>
@@ -4192,7 +12358,6 @@
           <t>Sokol Říčany</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>6</v>
       </c>
@@ -4239,16 +12404,11 @@
           <t>CLUB_S1948_49_0022</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>TR_S1948_49_00110</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4256,7 +12416,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>4</v>
       </c>
@@ -4265,7 +12424,6 @@
           <t>Sokol Velké Popovice</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>6</v>
       </c>
@@ -4312,16 +12470,11 @@
           <t>CLUB_S1948_49_0023</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S1948_49_00111</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4329,7 +12482,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>5</v>
       </c>
@@ -4338,7 +12490,6 @@
           <t>Sokol Modrobílí Kolín</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>6</v>
       </c>
@@ -4385,16 +12536,11 @@
           <t>CLUB_S1948_49_0024</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>TR_S1948_49_00112</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4402,7 +12548,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>6</v>
       </c>
@@ -4411,7 +12556,6 @@
           <t>Sokol Vršovice-Bohemians</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>6</v>
       </c>
@@ -4458,16 +12602,11 @@
           <t>CLUB_S1948_49_0025</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>TR_S1948_49_00113</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4475,7 +12614,6 @@
           <t>T</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>7</v>
       </c>
@@ -4484,7 +12622,6 @@
           <t>Sokol Čelákovice</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>6</v>
       </c>
@@ -4531,16 +12668,11 @@
           <t>CLUB_S1948_49_0026</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>TR_S1948_49_00114</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -4004,7 +4004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4048,9 +4048,77 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lektor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ZSEVC II.tř.A/sk.C · Sokol Dobrovice</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(žádné otevřené položky — sezóna OK)</t>
+          <t>Nesedí rozpis: GP=5, ale V+R+P=4 (1 zápas chybí). Ověřit z archivu/tisku.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lektor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZHORA II.tř./sk.C · Sokol Horácká Slavia Třebíč</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Body=2 při 2 výhrách (má být 4?). Překlep ve zdroji – ověřit.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lektor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ZHANA I.tř./sk.B · SK Podvesná</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Body=10 při 4 výhrách (2-1-0 → 8). Nesedí V nebo body – ověřit.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ne</t>
         </is>
       </c>
     </row>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -46,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -92,6 +101,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4004,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4121,6 +4132,240 @@
           <t>ne</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Podbrdská župa I.třída (Středočeský kraj) · NODE_S1948_49_0063</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Horymír Příbram), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kladenská župa II.třída / skupina C2 (Středočeský kraj) · NODE_S1948_49_0045</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Všetaty), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Podbrdská župa II.třída / skupina Hořovice (Středočeský kraj) · NODE_S1948_49_0065</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Sparta Podluhy), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Východočeská župa II.třída / skupina B (východní Čechy) · NODE_S1948_49_0101</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Sokol Heřmanův Městec, Spartak Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Západomoravská župa II.třída / skupina A (jihozápadní Morava) · NODE_S1948_49_0124</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Sokol Němčice u Ivančic, Sokol Žabčice), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Západomoravská župa II.třída / skupina B (jihozápadní Morava) · NODE_S1948_49_0125</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (SK Maloměřice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Západomoravská župa II.třída / skupina C (jihozápadní Morava) · NODE_S1948_49_0126</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (SK Nemojany), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Západomoravská župa II.třída / skupina D (jihozápadní Morava) · NODE_S1948_49_0127</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Břeclav), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Západomoravská župa II.třída / skupina E (jihozápadní Morava) · NODE_S1948_49_0128</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Bratčice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -103,6 +103,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4147,7 +4150,7 @@
           <t>Podbrdská župa I.třída (Středočeský kraj) · NODE_S1948_49_0063</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Horymír Příbram), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4173,7 +4176,7 @@
           <t>Kladenská župa II.třída / skupina C2 (Středočeský kraj) · NODE_S1948_49_0045</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Všetaty), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4199,7 +4202,7 @@
           <t>Podbrdská župa II.třída / skupina Hořovice (Středočeský kraj) · NODE_S1948_49_0065</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Sparta Podluhy), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4225,7 +4228,7 @@
           <t>Východočeská župa II.třída / skupina B (východní Čechy) · NODE_S1948_49_0101</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Sokol Heřmanův Městec, Spartak Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -4251,7 +4254,7 @@
           <t>Západomoravská župa II.třída / skupina A (jihozápadní Morava) · NODE_S1948_49_0124</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Sokol Němčice u Ivančic, Sokol Žabčice), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -4277,7 +4280,7 @@
           <t>Západomoravská župa II.třída / skupina B (jihozápadní Morava) · NODE_S1948_49_0125</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (SK Maloměřice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4303,7 +4306,7 @@
           <t>Západomoravská župa II.třída / skupina C (jihozápadní Morava) · NODE_S1948_49_0126</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (SK Nemojany), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4329,7 +4332,7 @@
           <t>Západomoravská župa II.třída / skupina D (jihozápadní Morava) · NODE_S1948_49_0127</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Břeclav), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -4355,7 +4358,7 @@
           <t>Západomoravská župa II.třída / skupina E (jihozápadní Morava) · NODE_S1948_49_0128</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Bratčice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -69730,13 +69733,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_text</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fake_club_ids</t>
         </is>
       </c>
     </row>
@@ -69982,6 +70005,159 @@
       <c r="A36" t="inlineStr">
         <is>
           <t>Středočeská župa – II.třída / skupiny H až K: výsledek: Sokol Nusle III – Sokol Strašnice II 9:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Horymír Příbram), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0063</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Všetaty), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0045</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Sparta Podluhy), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0065</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Sokol Heřmanův Městec, Spartak Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0101</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Sokol Němčice u Ivančic, Sokol Žabčice), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0124</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (SK Maloměřice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0125</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (SK Nemojany), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0126</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Břeclav), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0127</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Bratčice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NODE_S1948_49_0128</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -18719,7 +18719,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30_Středočeská divize</t>
+          <t>Středočeská divize</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30_Středočeská divize Skupina A</t>
+          <t>Středočeská divize Skupina A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30_Středočeská divize Skupina B</t>
+          <t>Středočeská divize Skupina B</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30_Západočeská divize</t>
+          <t>Západočeská divize</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30_Západočeská Skupina A</t>
+          <t>Západočeská Skupina A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30_Západočeská Skupina B</t>
+          <t>Západočeská Skupina B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30_Východočeská divize</t>
+          <t>Východočeská divize</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30_Východočeská Skupina A</t>
+          <t>Východočeská Skupina A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30_Východočeská Skupina B</t>
+          <t>Východočeská Skupina B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30_Moravskoslezská divize</t>
+          <t>Moravskoslezská divize</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30_Moravskoslezská Skupina A</t>
+          <t>Moravskoslezská Skupina A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30_Moravskoslezská Skupina B</t>
+          <t>Moravskoslezská Skupina B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30_Slovenská oblastná liga divize</t>
+          <t>Slovenská oblastná liga divize</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30_Slovenská oblastná liga Skupina západ</t>
+          <t>Slovenská oblastná liga Skupina západ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30_Slovenská oblastná liga Skupina východ</t>
+          <t>Slovenská oblastná liga Skupina východ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/data/S1948_49_FINAL.xlsx
+++ b/data/S1948_49_FINAL.xlsx
@@ -3292,6 +3292,11 @@
           <t>CLUB_S1948_49_0033</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>play off</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>TR_S1948_49_00248</t>
@@ -3356,6 +3361,11 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>CLUB_S1948_49_0040</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
